--- a/artfynd/A 30950-2026 artfynd.xlsx
+++ b/artfynd/A 30950-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971329</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971333</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971328</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971332</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971343</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971427</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971327</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971340</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971341</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971430</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129155699</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,8 +1956,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129412796</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30950-2026 artfynd.xlsx
+++ b/artfynd/A 30950-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,45 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128971328</v>
+        <v>136164356</v>
       </c>
       <c r="B4" t="n">
-        <v>79864</v>
+        <v>92076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1352</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+          <t>Tallbergssluttningarna NR, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715499</v>
+        <v>715508</v>
       </c>
       <c r="R4" t="n">
-        <v>7079716</v>
+        <v>7079714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,13 +995,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128971328</t>
+          <t>https://artportalen.se/Sighting/136164356</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128971332</v>
+        <v>128971328</v>
       </c>
       <c r="B5" t="n">
         <v>79864</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715507</v>
+        <v>715499</v>
       </c>
       <c r="R5" t="n">
-        <v>7079711</v>
+        <v>7079716</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,13 +1102,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128971332</t>
+          <t>https://artportalen.se/Sighting/128971328</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128971343</v>
+        <v>128971332</v>
       </c>
       <c r="B6" t="n">
         <v>79864</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715546</v>
+        <v>715507</v>
       </c>
       <c r="R6" t="n">
-        <v>7079627</v>
+        <v>7079711</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,38 +1209,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128971343</t>
+          <t>https://artportalen.se/Sighting/128971332</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128971427</v>
+        <v>128971343</v>
       </c>
       <c r="B7" t="n">
-        <v>96338</v>
+        <v>79864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>1352</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>715786</v>
+        <v>715546</v>
       </c>
       <c r="R7" t="n">
-        <v>7079789</v>
+        <v>7079627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,6 +1297,11 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1311,51 +1316,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128971427</t>
+          <t>https://artportalen.se/Sighting/128971343</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128971327</v>
+        <v>136164355</v>
       </c>
       <c r="B8" t="n">
-        <v>80461</v>
+        <v>79981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1352</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+          <t>Tallbergssluttningarna NR, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715509</v>
+        <v>715508</v>
       </c>
       <c r="R8" t="n">
-        <v>7079738</v>
+        <v>7079714</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,12 +1387,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1401,7 +1406,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1418,60 +1423,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128971327</t>
+          <t>https://artportalen.se/Sighting/136164355</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128971340</v>
+        <v>136164360</v>
       </c>
       <c r="B9" t="n">
-        <v>4775</v>
+        <v>79981</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>1352</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+          <t>Tallbergssluttningarna NR, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>715515</v>
       </c>
       <c r="R9" t="n">
-        <v>7079671</v>
+        <v>7079729</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,12 +1494,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,13 +1508,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>död gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1535,60 +1530,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128971340</t>
+          <t>https://artportalen.se/Sighting/136164360</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128971341</v>
+        <v>136164366</v>
       </c>
       <c r="B10" t="n">
-        <v>5179</v>
+        <v>79981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>1352</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+          <t>Tallbergssluttningarna NR, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715515</v>
+        <v>715555</v>
       </c>
       <c r="R10" t="n">
-        <v>7079671</v>
+        <v>7079769</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,12 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,13 +1615,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>död gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1652,51 +1637,51 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128971341</t>
+          <t>https://artportalen.se/Sighting/136164366</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128971430</v>
+        <v>136164397</v>
       </c>
       <c r="B11" t="n">
-        <v>106228</v>
+        <v>79981</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>1352</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+          <t>Tallbergssluttningarna NR, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715781</v>
+        <v>715758</v>
       </c>
       <c r="R11" t="n">
-        <v>7079793</v>
+        <v>7079842</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,12 +1708,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,6 +1724,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1754,51 +1744,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128971430</t>
+          <t>https://artportalen.se/Sighting/136164397</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129155699</v>
+        <v>136164448</v>
       </c>
       <c r="B12" t="n">
-        <v>106228</v>
+        <v>79981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>1352</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+          <t>Tallbergssluttningarna NR, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715790</v>
+        <v>715580</v>
       </c>
       <c r="R12" t="n">
-        <v>7079817</v>
+        <v>7079648</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,12 +1815,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,6 +1831,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1856,16 +1851,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129155699</t>
+          <t>https://artportalen.se/Sighting/136164448</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129412796</v>
+        <v>128971427</v>
       </c>
       <c r="B13" t="n">
-        <v>106228</v>
+        <v>96338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715800</v>
+        <v>715786</v>
       </c>
       <c r="R13" t="n">
-        <v>7079829</v>
+        <v>7079789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,12 +1922,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,13 +1947,2414 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Henrik Sporrong, Anna Hallmén, Julia Pettersson, Jonas F Grahn, Simon Mattsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/128971427</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136164445</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92028</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>715611</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7079652</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164445</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136164447</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92028</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>715584</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7079657</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164447</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128971327</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>715509</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7079738</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971327</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128971340</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>715515</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7079671</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971340</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128971341</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>715515</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7079671</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971341</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136164444</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>715611</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7079652</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164444</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136164446</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219851</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Hässlebrodd</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Milium effusum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>715593</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7079657</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164446</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136164408</v>
+      </c>
+      <c r="B21" t="n">
+        <v>108319</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>715727</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7079801</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164408</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136164412</v>
+      </c>
+      <c r="B22" t="n">
+        <v>108319</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>715722</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7079795</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164412</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136164455</v>
+      </c>
+      <c r="B23" t="n">
+        <v>108319</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>715580</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7079639</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164455</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128971430</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106228</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>715781</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7079793</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128971430</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129155699</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106228</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>715790</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7079817</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129155699</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129412796</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106228</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>N Per-Andersströcken, Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>715800</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7079829</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Henrik Sporrong, Anna Hallmén, Julia Pettersson, Jonas F Grahn, Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129412796</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136164451</v>
+      </c>
+      <c r="B27" t="n">
+        <v>103869</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>715579</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7079650</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164451</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136164396</v>
+      </c>
+      <c r="B28" t="n">
+        <v>104817</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>715761</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7079843</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164396</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136164399</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99571</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>715743</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7079839</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164399</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136164415</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99571</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>715733</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7079744</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164415</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136164450</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99571</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>715579</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7079650</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164450</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136164583</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99571</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>715830</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7079795</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164583</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136164398</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99100</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>715743</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7079839</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164398</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136164403</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99100</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>715740</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7079827</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164403</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136164406</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99100</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>715727</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7079804</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164406</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136164419</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99100</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tallbergssluttningarna NR, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>715737</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7079731</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136164419</t>
         </is>
       </c>
     </row>
@@ -1976,6 +4372,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30950-2026 artfynd.xlsx
+++ b/artfynd/A 30950-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136164356</v>
       </c>
       <c r="B4" t="n">
-        <v>92076</v>
+        <v>92077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136164445</v>
       </c>
       <c r="B14" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136164447</v>
       </c>
       <c r="B15" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136164446</v>
       </c>
       <c r="B20" t="n">
-        <v>100916</v>
+        <v>100917</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136164408</v>
       </c>
       <c r="B21" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136164412</v>
       </c>
       <c r="B22" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>136164455</v>
       </c>
       <c r="B23" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>136164451</v>
       </c>
       <c r="B27" t="n">
-        <v>103869</v>
+        <v>103870</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>136164396</v>
       </c>
       <c r="B28" t="n">
-        <v>104817</v>
+        <v>104818</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>136164399</v>
       </c>
       <c r="B29" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136164415</v>
       </c>
       <c r="B30" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136164450</v>
       </c>
       <c r="B31" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>136164583</v>
       </c>
       <c r="B32" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136164398</v>
       </c>
       <c r="B33" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>136164403</v>
       </c>
       <c r="B34" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136164406</v>
       </c>
       <c r="B35" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>136164419</v>
       </c>
       <c r="B36" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30950-2026 artfynd.xlsx
+++ b/artfynd/A 30950-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136164356</v>
       </c>
       <c r="B4" t="n">
-        <v>92077</v>
+        <v>92078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>136164355</v>
       </c>
       <c r="B8" t="n">
-        <v>79981</v>
+        <v>79982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>136164360</v>
       </c>
       <c r="B9" t="n">
-        <v>79981</v>
+        <v>79982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136164366</v>
       </c>
       <c r="B10" t="n">
-        <v>79981</v>
+        <v>79982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136164397</v>
       </c>
       <c r="B11" t="n">
-        <v>79981</v>
+        <v>79982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136164448</v>
       </c>
       <c r="B12" t="n">
-        <v>79981</v>
+        <v>79982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136164445</v>
       </c>
       <c r="B14" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136164447</v>
       </c>
       <c r="B15" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136164446</v>
       </c>
       <c r="B20" t="n">
-        <v>100917</v>
+        <v>100918</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136164408</v>
       </c>
       <c r="B21" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136164412</v>
       </c>
       <c r="B22" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>136164455</v>
       </c>
       <c r="B23" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>136164451</v>
       </c>
       <c r="B27" t="n">
-        <v>103870</v>
+        <v>103871</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>136164396</v>
       </c>
       <c r="B28" t="n">
-        <v>104818</v>
+        <v>104819</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>136164399</v>
       </c>
       <c r="B29" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136164415</v>
       </c>
       <c r="B30" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136164450</v>
       </c>
       <c r="B31" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>136164583</v>
       </c>
       <c r="B32" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136164398</v>
       </c>
       <c r="B33" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>136164403</v>
       </c>
       <c r="B34" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136164406</v>
       </c>
       <c r="B35" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>136164419</v>
       </c>
       <c r="B36" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30950-2026 artfynd.xlsx
+++ b/artfynd/A 30950-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136164356</v>
       </c>
       <c r="B4" t="n">
-        <v>92078</v>
+        <v>92084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>136164355</v>
       </c>
       <c r="B8" t="n">
-        <v>79982</v>
+        <v>79986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>136164360</v>
       </c>
       <c r="B9" t="n">
-        <v>79982</v>
+        <v>79986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136164366</v>
       </c>
       <c r="B10" t="n">
-        <v>79982</v>
+        <v>79986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136164397</v>
       </c>
       <c r="B11" t="n">
-        <v>79982</v>
+        <v>79986</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136164448</v>
       </c>
       <c r="B12" t="n">
-        <v>79982</v>
+        <v>79986</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136164445</v>
       </c>
       <c r="B14" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136164447</v>
       </c>
       <c r="B15" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136164446</v>
       </c>
       <c r="B20" t="n">
-        <v>100918</v>
+        <v>100924</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136164408</v>
       </c>
       <c r="B21" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136164412</v>
       </c>
       <c r="B22" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>136164455</v>
       </c>
       <c r="B23" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>136164451</v>
       </c>
       <c r="B27" t="n">
-        <v>103871</v>
+        <v>103877</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>136164396</v>
       </c>
       <c r="B28" t="n">
-        <v>104819</v>
+        <v>104825</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>136164399</v>
       </c>
       <c r="B29" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136164415</v>
       </c>
       <c r="B30" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136164450</v>
       </c>
       <c r="B31" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>136164583</v>
       </c>
       <c r="B32" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136164398</v>
       </c>
       <c r="B33" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>136164403</v>
       </c>
       <c r="B34" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136164406</v>
       </c>
       <c r="B35" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>136164419</v>
       </c>
       <c r="B36" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30950-2026 artfynd.xlsx
+++ b/artfynd/A 30950-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136164356</v>
       </c>
       <c r="B4" t="n">
-        <v>92084</v>
+        <v>92085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>136164355</v>
       </c>
       <c r="B8" t="n">
-        <v>79986</v>
+        <v>79987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>136164360</v>
       </c>
       <c r="B9" t="n">
-        <v>79986</v>
+        <v>79987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136164366</v>
       </c>
       <c r="B10" t="n">
-        <v>79986</v>
+        <v>79987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136164397</v>
       </c>
       <c r="B11" t="n">
-        <v>79986</v>
+        <v>79987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>136164448</v>
       </c>
       <c r="B12" t="n">
-        <v>79986</v>
+        <v>79987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136164445</v>
       </c>
       <c r="B14" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136164447</v>
       </c>
       <c r="B15" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136164446</v>
       </c>
       <c r="B20" t="n">
-        <v>100924</v>
+        <v>100925</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136164408</v>
       </c>
       <c r="B21" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136164412</v>
       </c>
       <c r="B22" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>136164455</v>
       </c>
       <c r="B23" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>136164451</v>
       </c>
       <c r="B27" t="n">
-        <v>103877</v>
+        <v>103878</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>136164396</v>
       </c>
       <c r="B28" t="n">
-        <v>104825</v>
+        <v>104826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>136164399</v>
       </c>
       <c r="B29" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>136164415</v>
       </c>
       <c r="B30" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>136164450</v>
       </c>
       <c r="B31" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>136164583</v>
       </c>
       <c r="B32" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136164398</v>
       </c>
       <c r="B33" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>136164403</v>
       </c>
       <c r="B34" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136164406</v>
       </c>
       <c r="B35" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>136164419</v>
       </c>
       <c r="B36" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
